--- a/static/Жилые_Комплексы/ЖК_Бахор/price_shaxamtka.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/price_shaxamtka.xlsx
@@ -46,12 +46,18 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -64,16 +70,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -90,16 +96,16 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="9" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -119,6 +125,7 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
     </indexedColors>
   </colors>
@@ -318,17 +325,17 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -355,10 +362,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Arial"/>
-            <a:ea typeface="Arial"/>
-            <a:cs typeface="Arial"/>
-            <a:sym typeface="Arial"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -597,12 +604,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -879,7 +886,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -906,10 +913,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Arial"/>
-            <a:ea typeface="Arial"/>
-            <a:cs typeface="Arial"/>
-            <a:sym typeface="Arial"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1197,16 +1204,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="4">
+        <v>4000000</v>
+      </c>
+      <c r="C3" s="4">
         <v>4200000</v>
       </c>
-      <c r="C3" s="4">
+      <c r="D3" s="4">
         <v>4400000</v>
       </c>
-      <c r="D3" s="4">
+      <c r="E3" s="4">
         <v>4600000</v>
-      </c>
-      <c r="E3" s="4">
-        <v>4800000</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
@@ -1214,13 +1221,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="4">
+        <v>4200000</v>
+      </c>
+      <c r="C4" s="4">
         <v>4400000</v>
       </c>
-      <c r="C4" s="4">
+      <c r="D4" s="4">
         <v>4600000</v>
-      </c>
-      <c r="D4" s="4">
-        <v>4800000</v>
       </c>
       <c r="E4" s="4">
         <v>4800000</v>
@@ -1231,10 +1238,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="4">
+        <v>4400000</v>
+      </c>
+      <c r="C5" s="4">
         <v>4600000</v>
-      </c>
-      <c r="C5" s="4">
-        <v>4800000</v>
       </c>
       <c r="D5" s="4">
         <v>4800000</v>
@@ -1248,7 +1255,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="4">
-        <v>4800000</v>
+        <v>4600000</v>
       </c>
       <c r="C6" s="4">
         <v>4800000</v>

--- a/static/Жилые_Комплексы/ЖК_Бахор/price_shaxamtka.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/price_shaxamtka.xlsx
@@ -1,54 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1">
-  <si>
-    <t>Этаж</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
+      <name val="Arial"/>
+      <color indexed="8"/>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Helvetica Neue"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color indexed="8"/>
       <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
+      <color indexed="8"/>
       <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -85,35 +77,35 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="ff000000"/>
@@ -1157,159 +1149,170 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6667" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="5" width="12.6719" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="12.6719" style="1" customWidth="1"/>
+    <col width="12.6719" customWidth="1" style="1" min="1" max="5"/>
+    <col width="12.6719" customWidth="1" style="1" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" t="s" s="2">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3">
+    <row r="1" ht="19.5" customHeight="1" s="6">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Этаж</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="3" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="4">
+    <row r="2" ht="19.5" customHeight="1" s="6">
+      <c r="A2" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B2" s="4">
-        <v>4000000</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="B2" s="4" t="n">
         <v>4200000</v>
       </c>
-      <c r="D2" s="4">
+      <c r="C2" s="4" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>4400000</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="4" t="n">
         <v>4600000</v>
       </c>
     </row>
-    <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="4">
+    <row r="3" ht="19.5" customHeight="1" s="6">
+      <c r="A3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B3" s="4">
-        <v>4000000</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="4" t="n">
         <v>4200000</v>
       </c>
-      <c r="D3" s="4">
+      <c r="C3" s="4" t="n">
         <v>4400000</v>
       </c>
-      <c r="E3" s="4">
+      <c r="D3" s="4" t="n">
         <v>4600000</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>4800000</v>
+      </c>
     </row>
-    <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="4">
+    <row r="4" ht="19.5" customHeight="1" s="6">
+      <c r="A4" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B4" s="4">
-        <v>4200000</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="B4" s="4" t="n">
         <v>4400000</v>
       </c>
-      <c r="D4" s="4">
+      <c r="C4" s="4" t="n">
         <v>4600000</v>
       </c>
-      <c r="E4" s="4">
+      <c r="D4" s="4" t="n">
         <v>4800000</v>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>5000000</v>
+      </c>
     </row>
-    <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="4">
+    <row r="5" ht="19.5" customHeight="1" s="6">
+      <c r="A5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
-        <v>4400000</v>
-      </c>
-      <c r="C5" s="4">
+      <c r="B5" s="4" t="n">
         <v>4600000</v>
       </c>
-      <c r="D5" s="4">
+      <c r="C5" s="4" t="n">
         <v>4800000</v>
       </c>
-      <c r="E5" s="4">
+      <c r="D5" s="4" t="n">
         <v>5000000</v>
       </c>
+      <c r="E5" s="4" t="n">
+        <v>5200000</v>
+      </c>
     </row>
-    <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="4">
+    <row r="6" ht="19.5" customHeight="1" s="6">
+      <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4">
-        <v>4600000</v>
-      </c>
-      <c r="C6" s="4">
+      <c r="B6" s="4" t="n">
         <v>4800000</v>
       </c>
-      <c r="D6" s="4">
+      <c r="C6" s="4" t="n">
         <v>5000000</v>
       </c>
-      <c r="E6" s="4">
+      <c r="D6" s="4" t="n">
         <v>5200000</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>5400000</v>
+      </c>
     </row>
-    <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="4">
+    <row r="7" ht="19.5" customHeight="1" s="6">
+      <c r="A7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="4">
-        <v>4800000</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="B7" s="4" t="n">
         <v>5000000</v>
       </c>
-      <c r="D7" s="4">
+      <c r="C7" s="4" t="n">
         <v>5200000</v>
       </c>
-      <c r="E7" s="4">
+      <c r="D7" s="4" t="n">
         <v>5400000</v>
       </c>
+      <c r="E7" s="4" t="n">
+        <v>5600000</v>
+      </c>
     </row>
-    <row r="8" ht="13.65" customHeight="1">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
+    <row r="8" ht="13.65" customHeight="1" s="6">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
     </row>
-    <row r="9" ht="13.65" customHeight="1">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+    <row r="9" ht="13.65" customHeight="1" s="6">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
     </row>
-    <row r="10" ht="13.65" customHeight="1">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
+    <row r="10" ht="13.65" customHeight="1" s="6">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
--- a/static/Жилые_Комплексы/ЖК_Бахор/price_shaxamtka.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/price_shaxamtka.xlsx
@@ -1188,13 +1188,13 @@
         <v>4200000</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4200000</v>
+        <v>4400000</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>4400000</v>
+        <v>4600000</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>4600000</v>
+        <v>4800000</v>
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1" s="6">
@@ -1202,16 +1202,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>4200000</v>
+        <v>4400000</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>4400000</v>
+        <v>4600000</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>4600000</v>
+        <v>4800000</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4800000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1" s="6">
@@ -1219,16 +1219,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4400000</v>
+        <v>4600000</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4600000</v>
+        <v>4800000</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>4800000</v>
+        <v>5000000</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5000000</v>
+        <v>5200000</v>
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1" s="6">
@@ -1236,16 +1236,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4600000</v>
+        <v>4800000</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4800000</v>
+        <v>5000000</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>5000000</v>
+        <v>5200000</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5200000</v>
+        <v>5400000</v>
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1" s="6">
@@ -1253,16 +1253,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4800000</v>
+        <v>5000000</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5000000</v>
+        <v>5200000</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5200000</v>
+        <v>5400000</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5400000</v>
+        <v>5600000</v>
       </c>
     </row>
     <row r="7" ht="19.5" customHeight="1" s="6">
@@ -1270,16 +1270,16 @@
         <v>1</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>5000000</v>
+        <v>5200000</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5200000</v>
+        <v>5400000</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5400000</v>
+        <v>5600000</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5600000</v>
+        <v>5800000</v>
       </c>
     </row>
     <row r="8" ht="13.65" customHeight="1" s="6">
